--- a/data/IK_Konj+Destatis_HWWI.xlsx
+++ b/data/IK_Konj+Destatis_HWWI.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l.mueller\Documents\FileCloud\Team Folders\IK_Server\Wirtschaft\statistische Daten\ik-dashboard\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87CD4957-9C1E-4746-9DA3-03076CC11340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -112,8 +106,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -172,25 +166,17 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -228,7 +214,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -262,7 +248,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -297,10 +282,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -473,11 +457,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:W46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -548,7 +532,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23">
       <c r="A2">
         <v>2015</v>
       </c>
@@ -556,13 +540,13 @@
         <v>23</v>
       </c>
       <c r="C2">
-        <v>151.16999999999999</v>
+        <v>151.17</v>
       </c>
       <c r="D2">
         <v>102</v>
       </c>
       <c r="E2">
-        <v>129.36000000000001</v>
+        <v>129.36</v>
       </c>
       <c r="F2">
         <v>231.7</v>
@@ -583,10 +567,10 @@
         <v>29.3</v>
       </c>
       <c r="O2">
-        <v>494.33333333333331</v>
+        <v>494.3333333333333</v>
       </c>
       <c r="P2">
-        <v>85415.666666666672</v>
+        <v>85415.66666666667</v>
       </c>
       <c r="Q2">
         <v>34801667</v>
@@ -610,7 +594,7 @@
         <v>882786333</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23">
       <c r="A3">
         <v>2015</v>
       </c>
@@ -618,10 +602,10 @@
         <v>24</v>
       </c>
       <c r="C3">
-        <v>163.22999999999999</v>
+        <v>163.23</v>
       </c>
       <c r="D3">
-        <v>98.71</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="E3">
         <v>151.29</v>
@@ -645,10 +629,10 @@
         <v>58.5</v>
       </c>
       <c r="O3">
-        <v>494.66666666666669</v>
+        <v>494.6666666666667</v>
       </c>
       <c r="P3">
-        <v>87143.333333333328</v>
+        <v>87143.33333333333</v>
       </c>
       <c r="Q3">
         <v>34417001</v>
@@ -672,7 +656,7 @@
         <v>921369999</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23">
       <c r="A4">
         <v>2015</v>
       </c>
@@ -683,7 +667,7 @@
         <v>140.46</v>
       </c>
       <c r="D4">
-        <v>93.26</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="E4">
         <v>121.89</v>
@@ -701,16 +685,16 @@
         <v>-33.9</v>
       </c>
       <c r="L4">
-        <v>-4.5999999999999996</v>
+        <v>-4.6</v>
       </c>
       <c r="N4">
         <v>60.2</v>
       </c>
       <c r="O4">
-        <v>494.33333333333331</v>
+        <v>494.3333333333333</v>
       </c>
       <c r="P4">
-        <v>88792.333333333328</v>
+        <v>88792.33333333333</v>
       </c>
       <c r="Q4">
         <v>35328334</v>
@@ -734,7 +718,7 @@
         <v>917048334</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23">
       <c r="A5">
         <v>2015</v>
       </c>
@@ -760,7 +744,7 @@
         <v>28</v>
       </c>
       <c r="K5">
-        <v>-4.9000000000000004</v>
+        <v>-4.9</v>
       </c>
       <c r="L5">
         <v>4</v>
@@ -769,10 +753,10 @@
         <v>55.3</v>
       </c>
       <c r="O5">
-        <v>493.66666666666669</v>
+        <v>493.6666666666667</v>
       </c>
       <c r="P5">
-        <v>88520.666666666672</v>
+        <v>88520.66666666667</v>
       </c>
       <c r="Q5">
         <v>34910000</v>
@@ -796,7 +780,7 @@
         <v>871193334</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23">
       <c r="A6">
         <v>2016</v>
       </c>
@@ -810,7 +794,7 @@
         <v>84.2</v>
       </c>
       <c r="E6">
-        <v>84.49</v>
+        <v>84.48999999999999</v>
       </c>
       <c r="F6">
         <v>142.32</v>
@@ -828,10 +812,10 @@
         <v>11.3</v>
       </c>
       <c r="N6">
-        <v>70.599999999999994</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="O6">
-        <v>503.66666666666669</v>
+        <v>503.6666666666667</v>
       </c>
       <c r="P6">
         <v>89736</v>
@@ -858,7 +842,7 @@
         <v>896210333</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23">
       <c r="A7">
         <v>2016</v>
       </c>
@@ -869,7 +853,7 @@
         <v>114.7</v>
       </c>
       <c r="D7">
-        <v>85.32</v>
+        <v>85.31999999999999</v>
       </c>
       <c r="E7">
         <v>109.96</v>
@@ -893,7 +877,7 @@
         <v>62.7</v>
       </c>
       <c r="O7">
-        <v>508.66666666666669</v>
+        <v>508.6666666666667</v>
       </c>
       <c r="P7">
         <v>90386</v>
@@ -920,7 +904,7 @@
         <v>969759000</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23">
       <c r="A8">
         <v>2016</v>
       </c>
@@ -937,7 +921,7 @@
         <v>111.14</v>
       </c>
       <c r="F8">
-        <v>143.69999999999999</v>
+        <v>143.7</v>
       </c>
       <c r="G8" t="s">
         <v>27</v>
@@ -958,7 +942,7 @@
         <v>510</v>
       </c>
       <c r="P8">
-        <v>91594.666666666686</v>
+        <v>91594.66666666669</v>
       </c>
       <c r="Q8">
         <v>36339000</v>
@@ -982,7 +966,7 @@
         <v>962288334</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23">
       <c r="A9">
         <v>2016</v>
       </c>
@@ -990,7 +974,7 @@
         <v>26</v>
       </c>
       <c r="C9">
-        <v>143.86000000000001</v>
+        <v>143.86</v>
       </c>
       <c r="D9">
         <v>151.25</v>
@@ -1011,7 +995,7 @@
         <v>-8</v>
       </c>
       <c r="L9">
-        <v>2.2999999999999998</v>
+        <v>2.3</v>
       </c>
       <c r="N9">
         <v>60.9</v>
@@ -1020,7 +1004,7 @@
         <v>509</v>
       </c>
       <c r="P9">
-        <v>91318.666666666686</v>
+        <v>91318.66666666669</v>
       </c>
       <c r="Q9">
         <v>35379667</v>
@@ -1044,7 +1028,7 @@
         <v>920080001</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23">
       <c r="A10">
         <v>2017</v>
       </c>
@@ -1079,10 +1063,10 @@
         <v>70</v>
       </c>
       <c r="O10">
-        <v>510.66666666666669</v>
+        <v>510.6666666666667</v>
       </c>
       <c r="P10">
-        <v>90882.666666666686</v>
+        <v>90882.66666666669</v>
       </c>
       <c r="Q10">
         <v>37728334</v>
@@ -1106,7 +1090,7 @@
         <v>987298333</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23">
       <c r="A11">
         <v>2017</v>
       </c>
@@ -1138,13 +1122,13 @@
         <v>-4</v>
       </c>
       <c r="N11">
-        <v>78.400000000000006</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="O11">
-        <v>515.33333333333337</v>
+        <v>515.3333333333334</v>
       </c>
       <c r="P11">
-        <v>91548.666666666686</v>
+        <v>91548.66666666669</v>
       </c>
       <c r="Q11">
         <v>36063000</v>
@@ -1168,7 +1152,7 @@
         <v>1041335000</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23">
       <c r="A12">
         <v>2017</v>
       </c>
@@ -1179,7 +1163,7 @@
         <v>129.72</v>
       </c>
       <c r="D12">
-        <v>139.27000000000001</v>
+        <v>139.27</v>
       </c>
       <c r="E12">
         <v>117.2</v>
@@ -1206,7 +1190,7 @@
         <v>513</v>
       </c>
       <c r="P12">
-        <v>92896.333333333314</v>
+        <v>92896.33333333331</v>
       </c>
       <c r="Q12">
         <v>36435333</v>
@@ -1230,7 +1214,7 @@
         <v>1037990667</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23">
       <c r="A13">
         <v>2017</v>
       </c>
@@ -1244,7 +1228,7 @@
         <v>147.26</v>
       </c>
       <c r="E13">
-        <v>137.94999999999999</v>
+        <v>137.95</v>
       </c>
       <c r="F13">
         <v>219.21</v>
@@ -1262,10 +1246,10 @@
         <v>9.1</v>
       </c>
       <c r="N13">
-        <v>86.1</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="O13">
-        <v>512.33333333333337</v>
+        <v>512.3333333333334</v>
       </c>
       <c r="P13">
         <v>92995</v>
@@ -1292,7 +1276,7 @@
         <v>966161334</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23">
       <c r="A14">
         <v>2018</v>
       </c>
@@ -1300,10 +1284,10 @@
         <v>23</v>
       </c>
       <c r="C14">
-        <v>159.63999999999999</v>
+        <v>159.64</v>
       </c>
       <c r="D14">
-        <v>145.83000000000001</v>
+        <v>145.83</v>
       </c>
       <c r="E14">
         <v>144.63</v>
@@ -1324,13 +1308,13 @@
         <v>15</v>
       </c>
       <c r="N14">
-        <v>89.1</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="O14">
         <v>510</v>
       </c>
       <c r="P14">
-        <v>95069.666666666686</v>
+        <v>95069.66666666669</v>
       </c>
       <c r="Q14">
         <v>38554333</v>
@@ -1354,7 +1338,7 @@
         <v>1046669667</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23">
       <c r="A15">
         <v>2018</v>
       </c>
@@ -1380,7 +1364,7 @@
         <v>28</v>
       </c>
       <c r="K15">
-        <v>9.8000000000000007</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L15">
         <v>19.8</v>
@@ -1389,7 +1373,7 @@
         <v>85.5</v>
       </c>
       <c r="O15">
-        <v>512.66666666666663</v>
+        <v>512.6666666666666</v>
       </c>
       <c r="P15">
         <v>95527</v>
@@ -1416,7 +1400,7 @@
         <v>1084889666</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23">
       <c r="A16">
         <v>2018</v>
       </c>
@@ -1451,7 +1435,7 @@
         <v>78</v>
       </c>
       <c r="O16">
-        <v>514.66666666666663</v>
+        <v>514.6666666666666</v>
       </c>
       <c r="P16">
         <v>97077</v>
@@ -1478,7 +1462,7 @@
         <v>1051112334</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23">
       <c r="A17">
         <v>2018</v>
       </c>
@@ -1492,7 +1476,7 @@
         <v>160.88</v>
       </c>
       <c r="E17">
-        <v>157.97999999999999</v>
+        <v>157.98</v>
       </c>
       <c r="F17">
         <v>261.83</v>
@@ -1513,10 +1497,10 @@
         <v>75</v>
       </c>
       <c r="O17">
-        <v>513.66666666666663</v>
+        <v>513.6666666666666</v>
       </c>
       <c r="P17">
-        <v>96858.333333333314</v>
+        <v>96858.33333333331</v>
       </c>
       <c r="Q17">
         <v>36775667</v>
@@ -1540,7 +1524,7 @@
         <v>987400666</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23">
       <c r="A18">
         <v>2019</v>
       </c>
@@ -1569,16 +1553,16 @@
         <v>-13.1</v>
       </c>
       <c r="L18">
-        <v>-4.5999999999999996</v>
+        <v>-4.6</v>
       </c>
       <c r="N18">
         <v>59.4</v>
       </c>
       <c r="O18">
-        <v>513.66666666666663</v>
+        <v>513.6666666666666</v>
       </c>
       <c r="P18">
-        <v>94968.333333333314</v>
+        <v>94968.33333333331</v>
       </c>
       <c r="Q18">
         <v>38536999</v>
@@ -1602,7 +1586,7 @@
         <v>1041927334</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23">
       <c r="A19">
         <v>2019</v>
       </c>
@@ -1610,7 +1594,7 @@
         <v>24</v>
       </c>
       <c r="C19">
-        <v>152.88999999999999</v>
+        <v>152.89</v>
       </c>
       <c r="D19">
         <v>119.75</v>
@@ -1619,7 +1603,7 @@
         <v>160.96</v>
       </c>
       <c r="F19">
-        <v>138.36000000000001</v>
+        <v>138.36</v>
       </c>
       <c r="G19" t="s">
         <v>27</v>
@@ -1640,7 +1624,7 @@
         <v>520</v>
       </c>
       <c r="P19">
-        <v>95082.333333333314</v>
+        <v>95082.33333333331</v>
       </c>
       <c r="Q19">
         <v>36891000</v>
@@ -1664,7 +1648,7 @@
         <v>1053524667</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23">
       <c r="A20">
         <v>2019</v>
       </c>
@@ -1672,13 +1656,13 @@
         <v>25</v>
       </c>
       <c r="C20">
-        <v>135.44999999999999</v>
+        <v>135.45</v>
       </c>
       <c r="D20">
         <v>106.97</v>
       </c>
       <c r="E20">
-        <v>147.19999999999999</v>
+        <v>147.2</v>
       </c>
       <c r="F20">
         <v>108.4</v>
@@ -1690,7 +1674,7 @@
         <v>28</v>
       </c>
       <c r="K20">
-        <v>-17.399999999999999</v>
+        <v>-17.4</v>
       </c>
       <c r="L20">
         <v>-20.3</v>
@@ -1702,7 +1686,7 @@
         <v>520</v>
       </c>
       <c r="P20">
-        <v>95791.333333333314</v>
+        <v>95791.33333333331</v>
       </c>
       <c r="Q20">
         <v>37470000</v>
@@ -1726,7 +1710,7 @@
         <v>1069753333</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23">
       <c r="A21">
         <v>2019</v>
       </c>
@@ -1743,7 +1727,7 @@
         <v>148.96</v>
       </c>
       <c r="F21">
-        <v>135.02000000000001</v>
+        <v>135.02</v>
       </c>
       <c r="G21" t="s">
         <v>27</v>
@@ -1752,7 +1736,7 @@
         <v>28</v>
       </c>
       <c r="K21">
-        <v>-39.299999999999997</v>
+        <v>-39.3</v>
       </c>
       <c r="L21">
         <v>-35.1</v>
@@ -1761,10 +1745,10 @@
         <v>-7.1</v>
       </c>
       <c r="O21">
-        <v>519.66666666666663</v>
+        <v>519.6666666666666</v>
       </c>
       <c r="P21">
-        <v>94913.333333333314</v>
+        <v>94913.33333333331</v>
       </c>
       <c r="Q21">
         <v>35702666</v>
@@ -1788,7 +1772,7 @@
         <v>980959000</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23">
       <c r="A22">
         <v>2020</v>
       </c>
@@ -1823,10 +1807,10 @@
         <v>4.5</v>
       </c>
       <c r="O22">
-        <v>510.66666666666669</v>
+        <v>510.6666666666667</v>
       </c>
       <c r="P22">
-        <v>91198.666666666686</v>
+        <v>91198.66666666669</v>
       </c>
       <c r="Q22">
         <v>36901333</v>
@@ -1850,7 +1834,7 @@
         <v>1034652667</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23">
       <c r="A23">
         <v>2020</v>
       </c>
@@ -1861,7 +1845,7 @@
         <v>75.39</v>
       </c>
       <c r="D23">
-        <v>92.24</v>
+        <v>92.23999999999999</v>
       </c>
       <c r="E23">
         <v>79.73</v>
@@ -1894,7 +1878,7 @@
         <v>511</v>
       </c>
       <c r="P23">
-        <v>90453.666666666686</v>
+        <v>90453.66666666669</v>
       </c>
       <c r="Q23">
         <v>33309667</v>
@@ -1918,7 +1902,7 @@
         <v>947075000</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23">
       <c r="A24">
         <v>2020</v>
       </c>
@@ -1926,16 +1910,16 @@
         <v>25</v>
       </c>
       <c r="C24">
-        <v>93.46</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="D24">
-        <v>83.24</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="E24">
-        <v>97.9</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="F24">
-        <v>83.07</v>
+        <v>83.06999999999999</v>
       </c>
       <c r="G24" t="s">
         <v>27</v>
@@ -1944,7 +1928,7 @@
         <v>28</v>
       </c>
       <c r="J24">
-        <v>-32.700000000000003</v>
+        <v>-32.7</v>
       </c>
       <c r="K24">
         <v>-44.9</v>
@@ -1956,13 +1940,13 @@
         <v>12.1</v>
       </c>
       <c r="N24">
-        <v>-65.400000000000006</v>
+        <v>-65.40000000000001</v>
       </c>
       <c r="O24">
-        <v>509.33333333333331</v>
+        <v>509.3333333333333</v>
       </c>
       <c r="P24">
-        <v>90486.333333333314</v>
+        <v>90486.33333333331</v>
       </c>
       <c r="Q24">
         <v>34561333</v>
@@ -1986,7 +1970,7 @@
         <v>1009566333</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23">
       <c r="A25">
         <v>2020</v>
       </c>
@@ -2024,10 +2008,10 @@
         <v>7.8</v>
       </c>
       <c r="N25">
-        <v>-36.200000000000003</v>
+        <v>-36.2</v>
       </c>
       <c r="O25">
-        <v>507.66666666666669</v>
+        <v>507.6666666666667</v>
       </c>
       <c r="P25">
         <v>90082</v>
@@ -2054,7 +2038,7 @@
         <v>1003897334</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23">
       <c r="A26">
         <v>2021</v>
       </c>
@@ -2062,7 +2046,7 @@
         <v>23</v>
       </c>
       <c r="C26">
-        <v>148.55000000000001</v>
+        <v>148.55</v>
       </c>
       <c r="D26">
         <v>133.22</v>
@@ -2080,13 +2064,13 @@
         <v>28</v>
       </c>
       <c r="J26">
-        <v>-4.9000000000000004</v>
+        <v>-4.9</v>
       </c>
       <c r="K26">
         <v>-22.5</v>
       </c>
       <c r="L26">
-        <v>-17.600000000000001</v>
+        <v>-17.6</v>
       </c>
       <c r="M26">
         <v>-47.1</v>
@@ -2098,7 +2082,7 @@
         <v>502</v>
       </c>
       <c r="P26">
-        <v>90729.666666666686</v>
+        <v>90729.66666666669</v>
       </c>
       <c r="Q26">
         <v>36965999</v>
@@ -2122,7 +2106,7 @@
         <v>1136444667</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23">
       <c r="A27">
         <v>2021</v>
       </c>
@@ -2160,13 +2144,13 @@
         <v>-82.8</v>
       </c>
       <c r="N27">
-        <v>5.0999999999999996</v>
+        <v>5.1</v>
       </c>
       <c r="O27">
-        <v>502.33333333333331</v>
+        <v>502.3333333333333</v>
       </c>
       <c r="P27">
-        <v>90940.666666666686</v>
+        <v>90940.66666666669</v>
       </c>
       <c r="Q27">
         <v>35490667</v>
@@ -2190,7 +2174,7 @@
         <v>1251811667</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23">
       <c r="A28">
         <v>2021</v>
       </c>
@@ -2207,7 +2191,7 @@
         <v>164.04</v>
       </c>
       <c r="F28">
-        <v>515.91999999999996</v>
+        <v>515.92</v>
       </c>
       <c r="G28" t="s">
         <v>27</v>
@@ -2234,7 +2218,7 @@
         <v>502</v>
       </c>
       <c r="P28">
-        <v>91740.666666666686</v>
+        <v>91740.66666666669</v>
       </c>
       <c r="Q28">
         <v>35435001</v>
@@ -2258,7 +2242,7 @@
         <v>1301976000</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23">
       <c r="A29">
         <v>2021</v>
       </c>
@@ -2269,7 +2253,7 @@
         <v>382.66</v>
       </c>
       <c r="D29">
-        <v>275.83999999999997</v>
+        <v>275.84</v>
       </c>
       <c r="E29">
         <v>183.89</v>
@@ -2293,7 +2277,7 @@
         <v>-8.1</v>
       </c>
       <c r="M29">
-        <v>-2.2999999999999998</v>
+        <v>-2.3</v>
       </c>
       <c r="N29">
         <v>33</v>
@@ -2302,7 +2286,7 @@
         <v>501</v>
       </c>
       <c r="P29">
-        <v>92002.666666666686</v>
+        <v>92002.66666666669</v>
       </c>
       <c r="Q29">
         <v>34791000</v>
@@ -2326,7 +2310,7 @@
         <v>1233235667</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23">
       <c r="A30">
         <v>2022</v>
       </c>
@@ -2343,7 +2327,7 @@
         <v>230.86</v>
       </c>
       <c r="F30">
-        <v>1069.3900000000001</v>
+        <v>1069.39</v>
       </c>
       <c r="G30" t="s">
         <v>27</v>
@@ -2394,7 +2378,7 @@
         <v>1366293000</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23">
       <c r="A31">
         <v>2022</v>
       </c>
@@ -2405,7 +2389,7 @@
         <v>477.66</v>
       </c>
       <c r="D31">
-        <v>580.16999999999996</v>
+        <v>580.17</v>
       </c>
       <c r="E31">
         <v>277.8</v>
@@ -2429,16 +2413,16 @@
         <v>-45.5</v>
       </c>
       <c r="M31">
-        <v>-76.900000000000006</v>
+        <v>-76.90000000000001</v>
       </c>
       <c r="N31">
         <v>-12.6</v>
       </c>
       <c r="O31">
-        <v>509.66666666666669</v>
+        <v>509.6666666666667</v>
       </c>
       <c r="P31">
-        <v>93034.333333333314</v>
+        <v>93034.33333333331</v>
       </c>
       <c r="Q31">
         <v>35705334</v>
@@ -2462,7 +2446,7 @@
         <v>1420781667</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23">
       <c r="A32">
         <v>2022</v>
       </c>
@@ -2476,7 +2460,7 @@
         <v>672.51</v>
       </c>
       <c r="E32">
-        <v>256.02999999999997</v>
+        <v>256.03</v>
       </c>
       <c r="F32">
         <v>2130.06</v>
@@ -2494,19 +2478,19 @@
         <v>-46.8</v>
       </c>
       <c r="L32">
-        <v>-34.299999999999997</v>
+        <v>-34.3</v>
       </c>
       <c r="M32">
-        <v>-17.399999999999999</v>
+        <v>-17.4</v>
       </c>
       <c r="N32">
         <v>-14.7</v>
       </c>
       <c r="O32">
-        <v>508.66666666666669</v>
+        <v>508.6666666666667</v>
       </c>
       <c r="P32">
-        <v>93600.333333333314</v>
+        <v>93600.33333333331</v>
       </c>
       <c r="Q32">
         <v>35585333</v>
@@ -2530,7 +2514,7 @@
         <v>1400780000</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:23">
       <c r="A33">
         <v>2022</v>
       </c>
@@ -2559,7 +2543,7 @@
         <v>-27.7</v>
       </c>
       <c r="K33">
-        <v>-77.099999999999994</v>
+        <v>-77.09999999999999</v>
       </c>
       <c r="L33">
         <v>-61.4</v>
@@ -2571,10 +2555,10 @@
         <v>-47</v>
       </c>
       <c r="O33">
-        <v>508.33333333333331</v>
+        <v>508.3333333333333</v>
       </c>
       <c r="P33">
-        <v>93135.333333333314</v>
+        <v>93135.33333333331</v>
       </c>
       <c r="Q33">
         <v>34132667</v>
@@ -2598,7 +2582,7 @@
         <v>1274810999</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:23">
       <c r="A34">
         <v>2023</v>
       </c>
@@ -2615,7 +2599,7 @@
         <v>202.06</v>
       </c>
       <c r="F34">
-        <v>566.32000000000005</v>
+        <v>566.3200000000001</v>
       </c>
       <c r="G34" t="s">
         <v>27</v>
@@ -2630,7 +2614,7 @@
         <v>-59.8</v>
       </c>
       <c r="L34">
-        <v>-40.799999999999997</v>
+        <v>-40.8</v>
       </c>
       <c r="M34">
         <v>21.2</v>
@@ -2666,7 +2650,7 @@
         <v>1324885333</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:23">
       <c r="A35">
         <v>2023</v>
       </c>
@@ -2707,10 +2691,10 @@
         <v>-20.7</v>
       </c>
       <c r="O35">
-        <v>519.66666666666663</v>
+        <v>519.6666666666666</v>
       </c>
       <c r="P35">
-        <v>92435.666666666686</v>
+        <v>92435.66666666669</v>
       </c>
       <c r="Q35">
         <v>34534333</v>
@@ -2734,7 +2718,7 @@
         <v>1235192001</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:23">
       <c r="A36">
         <v>2023</v>
       </c>
@@ -2778,7 +2762,7 @@
         <v>519</v>
       </c>
       <c r="P36">
-        <v>92216.333333333314</v>
+        <v>92216.33333333331</v>
       </c>
       <c r="Q36">
         <v>34677667</v>
@@ -2802,7 +2786,7 @@
         <v>1233688000</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:23">
       <c r="A37">
         <v>2023</v>
       </c>
@@ -2831,7 +2815,7 @@
         <v>-32.6</v>
       </c>
       <c r="K37">
-        <v>-67.400000000000006</v>
+        <v>-67.40000000000001</v>
       </c>
       <c r="L37">
         <v>-43.2</v>
@@ -2846,7 +2830,7 @@
         <v>518</v>
       </c>
       <c r="P37">
-        <v>91727.666666666686</v>
+        <v>91727.66666666669</v>
       </c>
       <c r="Q37">
         <v>33598333</v>
@@ -2870,7 +2854,7 @@
         <v>1156011000</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:23">
       <c r="A38">
         <v>2024</v>
       </c>
@@ -2887,7 +2871,7 @@
         <v>198.8</v>
       </c>
       <c r="F38">
-        <v>291.47000000000003</v>
+        <v>291.47</v>
       </c>
       <c r="G38" t="s">
         <v>27</v>
@@ -2914,7 +2898,7 @@
         <v>515</v>
       </c>
       <c r="P38">
-        <v>91036.666666666686</v>
+        <v>91036.66666666669</v>
       </c>
       <c r="Q38">
         <v>36093999</v>
@@ -2938,7 +2922,7 @@
         <v>1269569666</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:23">
       <c r="A39">
         <v>2024</v>
       </c>
@@ -2970,7 +2954,7 @@
         <v>-52.9</v>
       </c>
       <c r="L39">
-        <v>-19.399999999999999</v>
+        <v>-19.4</v>
       </c>
       <c r="M39">
         <v>-16.3</v>
@@ -2979,7 +2963,7 @@
         <v>-58.7</v>
       </c>
       <c r="O39">
-        <v>520.33333333333337</v>
+        <v>520.3333333333334</v>
       </c>
       <c r="P39">
         <v>91111</v>
@@ -3006,7 +2990,7 @@
         <v>1250462000</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:23">
       <c r="A40">
         <v>2024</v>
       </c>
@@ -3035,7 +3019,7 @@
         <v>-13.7</v>
       </c>
       <c r="K40">
-        <v>-39.200000000000003</v>
+        <v>-39.2</v>
       </c>
       <c r="L40">
         <v>-11</v>
@@ -3050,7 +3034,7 @@
         <v>519</v>
       </c>
       <c r="P40">
-        <v>91501.333333333314</v>
+        <v>91501.33333333331</v>
       </c>
       <c r="Q40">
         <v>34813000</v>
@@ -3074,7 +3058,7 @@
         <v>1266318001</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:23">
       <c r="A41">
         <v>2024</v>
       </c>
@@ -3115,10 +3099,10 @@
         <v>-53.8</v>
       </c>
       <c r="O41">
-        <v>518.33333333333337</v>
+        <v>518.3333333333334</v>
       </c>
       <c r="P41">
-        <v>91317.666666666686</v>
+        <v>91317.66666666669</v>
       </c>
       <c r="Q41">
         <v>33354000</v>
@@ -3142,7 +3126,7 @@
         <v>1171667333</v>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:23">
       <c r="A42">
         <v>2025</v>
       </c>
@@ -3171,22 +3155,22 @@
         <v>-17.39130434782609</v>
       </c>
       <c r="K42">
-        <v>-43.478260869565219</v>
+        <v>-43.47826086956522</v>
       </c>
       <c r="L42">
-        <v>-9.8901098901098905</v>
+        <v>-9.890109890109891</v>
       </c>
       <c r="M42">
-        <v>5.4347826086956523</v>
+        <v>5.434782608695652</v>
       </c>
       <c r="N42">
-        <v>-66.304347826086996</v>
+        <v>-66.304347826087</v>
       </c>
       <c r="O42">
-        <v>507.33333333333331</v>
+        <v>507.3333333333333</v>
       </c>
       <c r="P42">
-        <v>90690.333333333314</v>
+        <v>90690.33333333331</v>
       </c>
       <c r="Q42">
         <v>35355333</v>
@@ -3210,7 +3194,7 @@
         <v>1248682334</v>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:23">
       <c r="A43">
         <v>2025</v>
       </c>
@@ -3242,7 +3226,7 @@
         <v>-32.4</v>
       </c>
       <c r="L43">
-        <v>-8.6999999999999993</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="M43">
         <v>-6.7</v>
@@ -3254,7 +3238,7 @@
         <v>509</v>
       </c>
       <c r="P43">
-        <v>90306.666666666686</v>
+        <v>90306.66666666669</v>
       </c>
       <c r="Q43">
         <v>34012667</v>
@@ -3278,7 +3262,7 @@
         <v>1230606667</v>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:23">
       <c r="A44">
         <v>2025</v>
       </c>
@@ -3310,7 +3294,7 @@
         <v>-4.45</v>
       </c>
       <c r="K44">
-        <v>-26.670000000000009</v>
+        <v>-26.67000000000001</v>
       </c>
       <c r="L44">
         <v>-18.39</v>
@@ -3322,10 +3306,10 @@
         <v>-40</v>
       </c>
       <c r="O44">
-        <v>509.66666666666669</v>
+        <v>509.6666666666667</v>
       </c>
       <c r="P44">
-        <v>90814.666666666686</v>
+        <v>90814.66666666669</v>
       </c>
       <c r="Q44">
         <v>34594000</v>
@@ -3349,7 +3333,7 @@
         <v>1236617667</v>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:23">
       <c r="A45">
         <v>2025</v>
       </c>
@@ -3380,8 +3364,35 @@
       <c r="N45">
         <v>-55</v>
       </c>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="O45">
+        <v>509.6666666666667</v>
+      </c>
+      <c r="P45">
+        <v>90523.33333333331</v>
+      </c>
+      <c r="Q45">
+        <v>33269333</v>
+      </c>
+      <c r="R45">
+        <v>1270684666</v>
+      </c>
+      <c r="S45">
+        <v>5814783000</v>
+      </c>
+      <c r="T45">
+        <v>3043982667</v>
+      </c>
+      <c r="U45">
+        <v>2770801334</v>
+      </c>
+      <c r="V45">
+        <v>1611543333</v>
+      </c>
+      <c r="W45">
+        <v>1159257000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23">
       <c r="A46">
         <v>2026</v>
       </c>

--- a/data/IK_Konj+Destatis_HWWI.xlsx
+++ b/data/IK_Konj+Destatis_HWWI.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l.mueller\Documents\FileCloud\Team Folders\IK_Server\Wirtschaft\statistische Daten\ik-dashboard\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ACD8EA7-D094-4FAF-BF34-32568E28BE0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-28920" yWindow="2370" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="29">
   <si>
     <t>Jahr</t>
   </si>
@@ -106,8 +112,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -166,17 +172,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -214,7 +228,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -248,6 +262,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -282,9 +297,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -457,11 +473,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W46"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:W47"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -532,7 +548,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2015</v>
       </c>
@@ -540,16 +556,16 @@
         <v>23</v>
       </c>
       <c r="C2">
-        <v>151.17</v>
+        <v>151.27000000000001</v>
       </c>
       <c r="D2">
-        <v>102</v>
+        <v>102.05</v>
       </c>
       <c r="E2">
-        <v>129.36</v>
+        <v>129.43</v>
       </c>
       <c r="F2">
-        <v>231.7</v>
+        <v>231.91</v>
       </c>
       <c r="G2" t="s">
         <v>27</v>
@@ -567,10 +583,10 @@
         <v>29.3</v>
       </c>
       <c r="O2">
-        <v>494.3333333333333</v>
+        <v>494.33333333333331</v>
       </c>
       <c r="P2">
-        <v>85415.66666666667</v>
+        <v>85415.666666666672</v>
       </c>
       <c r="Q2">
         <v>34801667</v>
@@ -594,7 +610,7 @@
         <v>882786333</v>
       </c>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2015</v>
       </c>
@@ -602,16 +618,16 @@
         <v>24</v>
       </c>
       <c r="C3">
-        <v>163.23</v>
+        <v>163.35</v>
       </c>
       <c r="D3">
-        <v>98.70999999999999</v>
+        <v>98.77</v>
       </c>
       <c r="E3">
-        <v>151.29</v>
+        <v>151.38</v>
       </c>
       <c r="F3">
-        <v>218.52</v>
+        <v>218.75</v>
       </c>
       <c r="G3" t="s">
         <v>27</v>
@@ -629,10 +645,10 @@
         <v>58.5</v>
       </c>
       <c r="O3">
-        <v>494.6666666666667</v>
+        <v>494.66666666666669</v>
       </c>
       <c r="P3">
-        <v>87143.33333333333</v>
+        <v>87143.333333333328</v>
       </c>
       <c r="Q3">
         <v>34417001</v>
@@ -656,7 +672,7 @@
         <v>921369999</v>
       </c>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2015</v>
       </c>
@@ -664,16 +680,16 @@
         <v>25</v>
       </c>
       <c r="C4">
-        <v>140.46</v>
+        <v>140.52000000000001</v>
       </c>
       <c r="D4">
-        <v>93.26000000000001</v>
+        <v>93.28</v>
       </c>
       <c r="E4">
-        <v>121.89</v>
+        <v>121.93</v>
       </c>
       <c r="F4">
-        <v>210.61</v>
+        <v>210.75</v>
       </c>
       <c r="G4" t="s">
         <v>27</v>
@@ -685,16 +701,16 @@
         <v>-33.9</v>
       </c>
       <c r="L4">
-        <v>-4.6</v>
+        <v>-4.5999999999999996</v>
       </c>
       <c r="N4">
         <v>60.2</v>
       </c>
       <c r="O4">
-        <v>494.3333333333333</v>
+        <v>494.33333333333331</v>
       </c>
       <c r="P4">
-        <v>88792.33333333333</v>
+        <v>88792.333333333328</v>
       </c>
       <c r="Q4">
         <v>35328334</v>
@@ -718,7 +734,7 @@
         <v>917048334</v>
       </c>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2015</v>
       </c>
@@ -726,7 +742,7 @@
         <v>26</v>
       </c>
       <c r="C5">
-        <v>126.16</v>
+        <v>126.18</v>
       </c>
       <c r="D5">
         <v>86.02</v>
@@ -735,7 +751,7 @@
         <v>107.37</v>
       </c>
       <c r="F5">
-        <v>194.91</v>
+        <v>194.98</v>
       </c>
       <c r="G5" t="s">
         <v>27</v>
@@ -744,7 +760,7 @@
         <v>28</v>
       </c>
       <c r="K5">
-        <v>-4.9</v>
+        <v>-4.9000000000000004</v>
       </c>
       <c r="L5">
         <v>4</v>
@@ -753,10 +769,10 @@
         <v>55.3</v>
       </c>
       <c r="O5">
-        <v>493.6666666666667</v>
+        <v>493.66666666666669</v>
       </c>
       <c r="P5">
-        <v>88520.66666666667</v>
+        <v>88520.666666666672</v>
       </c>
       <c r="Q5">
         <v>34910000</v>
@@ -780,7 +796,7 @@
         <v>871193334</v>
       </c>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2016</v>
       </c>
@@ -788,16 +804,16 @@
         <v>23</v>
       </c>
       <c r="C6">
-        <v>97.86</v>
+        <v>97.94</v>
       </c>
       <c r="D6">
-        <v>84.2</v>
+        <v>84.26</v>
       </c>
       <c r="E6">
-        <v>84.48999999999999</v>
+        <v>84.55</v>
       </c>
       <c r="F6">
-        <v>142.32</v>
+        <v>142.46</v>
       </c>
       <c r="G6" t="s">
         <v>27</v>
@@ -812,10 +828,10 @@
         <v>11.3</v>
       </c>
       <c r="N6">
-        <v>70.59999999999999</v>
+        <v>70.599999999999994</v>
       </c>
       <c r="O6">
-        <v>503.6666666666667</v>
+        <v>503.66666666666669</v>
       </c>
       <c r="P6">
         <v>89736</v>
@@ -842,7 +858,7 @@
         <v>896210333</v>
       </c>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2016</v>
       </c>
@@ -850,16 +866,16 @@
         <v>24</v>
       </c>
       <c r="C7">
-        <v>114.7</v>
+        <v>114.73</v>
       </c>
       <c r="D7">
-        <v>85.31999999999999</v>
+        <v>85.33</v>
       </c>
       <c r="E7">
-        <v>109.96</v>
+        <v>109.98</v>
       </c>
       <c r="F7">
-        <v>137.76</v>
+        <v>137.84</v>
       </c>
       <c r="G7" t="s">
         <v>27</v>
@@ -877,7 +893,7 @@
         <v>62.7</v>
       </c>
       <c r="O7">
-        <v>508.6666666666667</v>
+        <v>508.66666666666669</v>
       </c>
       <c r="P7">
         <v>90386</v>
@@ -904,7 +920,7 @@
         <v>969759000</v>
       </c>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2016</v>
       </c>
@@ -912,16 +928,16 @@
         <v>25</v>
       </c>
       <c r="C8">
-        <v>118.35</v>
+        <v>118.28</v>
       </c>
       <c r="D8">
-        <v>106.4</v>
+        <v>106.33</v>
       </c>
       <c r="E8">
-        <v>111.14</v>
+        <v>111.06</v>
       </c>
       <c r="F8">
-        <v>143.7</v>
+        <v>143.66</v>
       </c>
       <c r="G8" t="s">
         <v>27</v>
@@ -942,7 +958,7 @@
         <v>510</v>
       </c>
       <c r="P8">
-        <v>91594.66666666669</v>
+        <v>91594.666666666686</v>
       </c>
       <c r="Q8">
         <v>36339000</v>
@@ -966,7 +982,7 @@
         <v>962288334</v>
       </c>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2016</v>
       </c>
@@ -974,16 +990,16 @@
         <v>26</v>
       </c>
       <c r="C9">
-        <v>143.86</v>
+        <v>143.88999999999999</v>
       </c>
       <c r="D9">
-        <v>151.25</v>
+        <v>151.26</v>
       </c>
       <c r="E9">
-        <v>125.28</v>
+        <v>125.3</v>
       </c>
       <c r="F9">
-        <v>197.8</v>
+        <v>197.89</v>
       </c>
       <c r="G9" t="s">
         <v>27</v>
@@ -995,7 +1011,7 @@
         <v>-8</v>
       </c>
       <c r="L9">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="N9">
         <v>60.9</v>
@@ -1004,7 +1020,7 @@
         <v>509</v>
       </c>
       <c r="P9">
-        <v>91318.66666666669</v>
+        <v>91318.666666666686</v>
       </c>
       <c r="Q9">
         <v>35379667</v>
@@ -1028,7 +1044,7 @@
         <v>920080001</v>
       </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2017</v>
       </c>
@@ -1036,16 +1052,16 @@
         <v>23</v>
       </c>
       <c r="C10">
-        <v>152.71</v>
+        <v>152.76</v>
       </c>
       <c r="D10">
-        <v>140.54</v>
+        <v>140.56</v>
       </c>
       <c r="E10">
-        <v>135.38</v>
+        <v>135.41</v>
       </c>
       <c r="F10">
-        <v>208.7</v>
+        <v>208.83</v>
       </c>
       <c r="G10" t="s">
         <v>27</v>
@@ -1063,10 +1079,10 @@
         <v>70</v>
       </c>
       <c r="O10">
-        <v>510.6666666666667</v>
+        <v>510.66666666666669</v>
       </c>
       <c r="P10">
-        <v>90882.66666666669</v>
+        <v>90882.666666666686</v>
       </c>
       <c r="Q10">
         <v>37728334</v>
@@ -1090,7 +1106,7 @@
         <v>987298333</v>
       </c>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2017</v>
       </c>
@@ -1098,13 +1114,13 @@
         <v>24</v>
       </c>
       <c r="C11">
-        <v>131.21</v>
+        <v>131.16999999999999</v>
       </c>
       <c r="D11">
-        <v>129.47</v>
+        <v>129.41999999999999</v>
       </c>
       <c r="E11">
-        <v>122.21</v>
+        <v>122.16</v>
       </c>
       <c r="F11">
         <v>158.94</v>
@@ -1122,13 +1138,13 @@
         <v>-4</v>
       </c>
       <c r="N11">
-        <v>78.40000000000001</v>
+        <v>78.400000000000006</v>
       </c>
       <c r="O11">
-        <v>515.3333333333334</v>
+        <v>515.33333333333337</v>
       </c>
       <c r="P11">
-        <v>91548.66666666669</v>
+        <v>91548.666666666686</v>
       </c>
       <c r="Q11">
         <v>36063000</v>
@@ -1152,7 +1168,7 @@
         <v>1041335000</v>
       </c>
     </row>
-    <row r="12" spans="1:23">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2017</v>
       </c>
@@ -1163,13 +1179,13 @@
         <v>129.72</v>
       </c>
       <c r="D12">
-        <v>139.27</v>
+        <v>139.25</v>
       </c>
       <c r="E12">
-        <v>117.2</v>
+        <v>117.19</v>
       </c>
       <c r="F12">
-        <v>164.73</v>
+        <v>164.77</v>
       </c>
       <c r="G12" t="s">
         <v>27</v>
@@ -1190,7 +1206,7 @@
         <v>513</v>
       </c>
       <c r="P12">
-        <v>92896.33333333331</v>
+        <v>92896.333333333314</v>
       </c>
       <c r="Q12">
         <v>36435333</v>
@@ -1214,7 +1230,7 @@
         <v>1037990667</v>
       </c>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2017</v>
       </c>
@@ -1222,16 +1238,16 @@
         <v>26</v>
       </c>
       <c r="C13">
-        <v>157.4</v>
+        <v>157.34</v>
       </c>
       <c r="D13">
-        <v>147.26</v>
+        <v>147.18</v>
       </c>
       <c r="E13">
-        <v>137.95</v>
+        <v>137.88</v>
       </c>
       <c r="F13">
-        <v>219.21</v>
+        <v>219.17</v>
       </c>
       <c r="G13" t="s">
         <v>27</v>
@@ -1246,10 +1262,10 @@
         <v>9.1</v>
       </c>
       <c r="N13">
-        <v>86.09999999999999</v>
+        <v>86.1</v>
       </c>
       <c r="O13">
-        <v>512.3333333333334</v>
+        <v>512.33333333333337</v>
       </c>
       <c r="P13">
         <v>92995</v>
@@ -1276,7 +1292,7 @@
         <v>966161334</v>
       </c>
     </row>
-    <row r="14" spans="1:23">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2018</v>
       </c>
@@ -1284,16 +1300,16 @@
         <v>23</v>
       </c>
       <c r="C14">
-        <v>159.64</v>
+        <v>159.55000000000001</v>
       </c>
       <c r="D14">
-        <v>145.83</v>
+        <v>145.74</v>
       </c>
       <c r="E14">
-        <v>144.63</v>
+        <v>144.53</v>
       </c>
       <c r="F14">
-        <v>209.11</v>
+        <v>209.05</v>
       </c>
       <c r="G14" t="s">
         <v>27</v>
@@ -1308,13 +1324,13 @@
         <v>15</v>
       </c>
       <c r="N14">
-        <v>89.09999999999999</v>
+        <v>89.1</v>
       </c>
       <c r="O14">
         <v>510</v>
       </c>
       <c r="P14">
-        <v>95069.66666666669</v>
+        <v>95069.666666666686</v>
       </c>
       <c r="Q14">
         <v>38554333</v>
@@ -1338,7 +1354,7 @@
         <v>1046669667</v>
       </c>
     </row>
-    <row r="15" spans="1:23">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2018</v>
       </c>
@@ -1346,16 +1362,16 @@
         <v>24</v>
       </c>
       <c r="C15">
-        <v>178.55</v>
+        <v>178.5</v>
       </c>
       <c r="D15">
-        <v>155.74</v>
+        <v>155.66999999999999</v>
       </c>
       <c r="E15">
-        <v>166.22</v>
+        <v>166.16</v>
       </c>
       <c r="F15">
-        <v>222.62</v>
+        <v>222.6</v>
       </c>
       <c r="G15" t="s">
         <v>27</v>
@@ -1364,7 +1380,7 @@
         <v>28</v>
       </c>
       <c r="K15">
-        <v>9.800000000000001</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="L15">
         <v>19.8</v>
@@ -1373,7 +1389,7 @@
         <v>85.5</v>
       </c>
       <c r="O15">
-        <v>512.6666666666666</v>
+        <v>512.66666666666663</v>
       </c>
       <c r="P15">
         <v>95527</v>
@@ -1400,7 +1416,7 @@
         <v>1084889666</v>
       </c>
     </row>
-    <row r="16" spans="1:23">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2018</v>
       </c>
@@ -1411,7 +1427,7 @@
         <v>192.67</v>
       </c>
       <c r="D16">
-        <v>171.45</v>
+        <v>171.44</v>
       </c>
       <c r="E16">
         <v>172.13</v>
@@ -1435,7 +1451,7 @@
         <v>78</v>
       </c>
       <c r="O16">
-        <v>514.6666666666666</v>
+        <v>514.66666666666663</v>
       </c>
       <c r="P16">
         <v>97077</v>
@@ -1462,7 +1478,7 @@
         <v>1051112334</v>
       </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2018</v>
       </c>
@@ -1470,13 +1486,13 @@
         <v>26</v>
       </c>
       <c r="C17">
-        <v>182.22</v>
+        <v>182.17</v>
       </c>
       <c r="D17">
-        <v>160.88</v>
+        <v>160.81</v>
       </c>
       <c r="E17">
-        <v>157.98</v>
+        <v>157.91999999999999</v>
       </c>
       <c r="F17">
         <v>261.83</v>
@@ -1497,10 +1513,10 @@
         <v>75</v>
       </c>
       <c r="O17">
-        <v>513.6666666666666</v>
+        <v>513.66666666666663</v>
       </c>
       <c r="P17">
-        <v>96858.33333333331</v>
+        <v>96858.333333333314</v>
       </c>
       <c r="Q17">
         <v>36775667</v>
@@ -1524,7 +1540,7 @@
         <v>987400666</v>
       </c>
     </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2019</v>
       </c>
@@ -1532,13 +1548,13 @@
         <v>23</v>
       </c>
       <c r="C18">
-        <v>159.06</v>
+        <v>159.05000000000001</v>
       </c>
       <c r="D18">
-        <v>145.74</v>
+        <v>145.72</v>
       </c>
       <c r="E18">
-        <v>148.03</v>
+        <v>148.01</v>
       </c>
       <c r="F18">
         <v>196.36</v>
@@ -1553,16 +1569,16 @@
         <v>-13.1</v>
       </c>
       <c r="L18">
-        <v>-4.6</v>
+        <v>-4.5999999999999996</v>
       </c>
       <c r="N18">
         <v>59.4</v>
       </c>
       <c r="O18">
-        <v>513.6666666666666</v>
+        <v>513.66666666666663</v>
       </c>
       <c r="P18">
-        <v>94968.33333333331</v>
+        <v>94968.333333333314</v>
       </c>
       <c r="Q18">
         <v>38536999</v>
@@ -1586,7 +1602,7 @@
         <v>1041927334</v>
       </c>
     </row>
-    <row r="19" spans="1:23">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2019</v>
       </c>
@@ -1594,16 +1610,16 @@
         <v>24</v>
       </c>
       <c r="C19">
-        <v>152.89</v>
+        <v>152.87</v>
       </c>
       <c r="D19">
-        <v>119.75</v>
+        <v>119.73</v>
       </c>
       <c r="E19">
-        <v>160.96</v>
+        <v>160.94</v>
       </c>
       <c r="F19">
-        <v>138.36</v>
+        <v>138.36000000000001</v>
       </c>
       <c r="G19" t="s">
         <v>27</v>
@@ -1624,7 +1640,7 @@
         <v>520</v>
       </c>
       <c r="P19">
-        <v>95082.33333333331</v>
+        <v>95082.333333333314</v>
       </c>
       <c r="Q19">
         <v>36891000</v>
@@ -1648,7 +1664,7 @@
         <v>1053524667</v>
       </c>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2019</v>
       </c>
@@ -1656,13 +1672,13 @@
         <v>25</v>
       </c>
       <c r="C20">
-        <v>135.45</v>
+        <v>135.49</v>
       </c>
       <c r="D20">
-        <v>106.97</v>
+        <v>107</v>
       </c>
       <c r="E20">
-        <v>147.2</v>
+        <v>147.26</v>
       </c>
       <c r="F20">
         <v>108.4</v>
@@ -1674,7 +1690,7 @@
         <v>28</v>
       </c>
       <c r="K20">
-        <v>-17.4</v>
+        <v>-17.399999999999999</v>
       </c>
       <c r="L20">
         <v>-20.3</v>
@@ -1686,7 +1702,7 @@
         <v>520</v>
       </c>
       <c r="P20">
-        <v>95791.33333333331</v>
+        <v>95791.333333333314</v>
       </c>
       <c r="Q20">
         <v>37470000</v>
@@ -1710,7 +1726,7 @@
         <v>1069753333</v>
       </c>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2019</v>
       </c>
@@ -1718,16 +1734,16 @@
         <v>26</v>
       </c>
       <c r="C21">
-        <v>143.37</v>
+        <v>143.38999999999999</v>
       </c>
       <c r="D21">
-        <v>114.69</v>
+        <v>114.7</v>
       </c>
       <c r="E21">
-        <v>148.96</v>
+        <v>148.97999999999999</v>
       </c>
       <c r="F21">
-        <v>135.02</v>
+        <v>135.02000000000001</v>
       </c>
       <c r="G21" t="s">
         <v>27</v>
@@ -1736,7 +1752,7 @@
         <v>28</v>
       </c>
       <c r="K21">
-        <v>-39.3</v>
+        <v>-39.299999999999997</v>
       </c>
       <c r="L21">
         <v>-35.1</v>
@@ -1745,10 +1761,10 @@
         <v>-7.1</v>
       </c>
       <c r="O21">
-        <v>519.6666666666666</v>
+        <v>519.66666666666663</v>
       </c>
       <c r="P21">
-        <v>94913.33333333331</v>
+        <v>94913.333333333314</v>
       </c>
       <c r="Q21">
         <v>35702666</v>
@@ -1772,7 +1788,7 @@
         <v>980959000</v>
       </c>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2020</v>
       </c>
@@ -1780,13 +1796,13 @@
         <v>23</v>
       </c>
       <c r="C22">
-        <v>117.56</v>
+        <v>117.53</v>
       </c>
       <c r="D22">
-        <v>120.25</v>
+        <v>120.22</v>
       </c>
       <c r="E22">
-        <v>122.15</v>
+        <v>122.11</v>
       </c>
       <c r="F22">
         <v>102.9</v>
@@ -1807,10 +1823,10 @@
         <v>4.5</v>
       </c>
       <c r="O22">
-        <v>510.6666666666667</v>
+        <v>510.66666666666669</v>
       </c>
       <c r="P22">
-        <v>91198.66666666669</v>
+        <v>91198.666666666686</v>
       </c>
       <c r="Q22">
         <v>36901333</v>
@@ -1834,7 +1850,7 @@
         <v>1034652667</v>
       </c>
     </row>
-    <row r="23" spans="1:23">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2020</v>
       </c>
@@ -1842,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="C23">
-        <v>75.39</v>
+        <v>75.430000000000007</v>
       </c>
       <c r="D23">
-        <v>92.23999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="E23">
-        <v>79.73</v>
+        <v>79.78</v>
       </c>
       <c r="F23">
         <v>57.24</v>
@@ -1878,7 +1894,7 @@
         <v>511</v>
       </c>
       <c r="P23">
-        <v>90453.66666666669</v>
+        <v>90453.666666666686</v>
       </c>
       <c r="Q23">
         <v>33309667</v>
@@ -1902,7 +1918,7 @@
         <v>947075000</v>
       </c>
     </row>
-    <row r="24" spans="1:23">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2020</v>
       </c>
@@ -1910,16 +1926,16 @@
         <v>25</v>
       </c>
       <c r="C24">
-        <v>93.45999999999999</v>
+        <v>93.46</v>
       </c>
       <c r="D24">
-        <v>83.23999999999999</v>
+        <v>83.24</v>
       </c>
       <c r="E24">
-        <v>97.90000000000001</v>
+        <v>97.9</v>
       </c>
       <c r="F24">
-        <v>83.06999999999999</v>
+        <v>83.07</v>
       </c>
       <c r="G24" t="s">
         <v>27</v>
@@ -1928,7 +1944,7 @@
         <v>28</v>
       </c>
       <c r="J24">
-        <v>-32.7</v>
+        <v>-32.700000000000003</v>
       </c>
       <c r="K24">
         <v>-44.9</v>
@@ -1940,13 +1956,13 @@
         <v>12.1</v>
       </c>
       <c r="N24">
-        <v>-65.40000000000001</v>
+        <v>-65.400000000000006</v>
       </c>
       <c r="O24">
-        <v>509.3333333333333</v>
+        <v>509.33333333333331</v>
       </c>
       <c r="P24">
-        <v>90486.33333333331</v>
+        <v>90486.333333333314</v>
       </c>
       <c r="Q24">
         <v>34561333</v>
@@ -1970,7 +1986,7 @@
         <v>1009566333</v>
       </c>
     </row>
-    <row r="25" spans="1:23">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2020</v>
       </c>
@@ -1978,13 +1994,13 @@
         <v>26</v>
       </c>
       <c r="C25">
-        <v>113.49</v>
+        <v>113.47</v>
       </c>
       <c r="D25">
-        <v>104.45</v>
+        <v>104.43</v>
       </c>
       <c r="E25">
-        <v>100.25</v>
+        <v>100.23</v>
       </c>
       <c r="F25">
         <v>156.18</v>
@@ -2008,10 +2024,10 @@
         <v>7.8</v>
       </c>
       <c r="N25">
-        <v>-36.2</v>
+        <v>-36.200000000000003</v>
       </c>
       <c r="O25">
-        <v>507.6666666666667</v>
+        <v>507.66666666666669</v>
       </c>
       <c r="P25">
         <v>90082</v>
@@ -2038,7 +2054,7 @@
         <v>1003897334</v>
       </c>
     </row>
-    <row r="26" spans="1:23">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2021</v>
       </c>
@@ -2046,13 +2062,13 @@
         <v>23</v>
       </c>
       <c r="C26">
-        <v>148.55</v>
+        <v>148.51</v>
       </c>
       <c r="D26">
-        <v>133.22</v>
+        <v>133.16</v>
       </c>
       <c r="E26">
-        <v>134.13</v>
+        <v>134.08000000000001</v>
       </c>
       <c r="F26">
         <v>196.7</v>
@@ -2064,13 +2080,13 @@
         <v>28</v>
       </c>
       <c r="J26">
-        <v>-4.9</v>
+        <v>-4.9000000000000004</v>
       </c>
       <c r="K26">
         <v>-22.5</v>
       </c>
       <c r="L26">
-        <v>-17.6</v>
+        <v>-17.600000000000001</v>
       </c>
       <c r="M26">
         <v>-47.1</v>
@@ -2082,7 +2098,7 @@
         <v>502</v>
       </c>
       <c r="P26">
-        <v>90729.66666666669</v>
+        <v>90729.666666666686</v>
       </c>
       <c r="Q26">
         <v>36965999</v>
@@ -2106,7 +2122,7 @@
         <v>1136444667</v>
       </c>
     </row>
-    <row r="27" spans="1:23">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2021</v>
       </c>
@@ -2117,7 +2133,7 @@
         <v>178.31</v>
       </c>
       <c r="D27">
-        <v>158.32</v>
+        <v>158.31</v>
       </c>
       <c r="E27">
         <v>151.22</v>
@@ -2144,13 +2160,13 @@
         <v>-82.8</v>
       </c>
       <c r="N27">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="O27">
-        <v>502.3333333333333</v>
+        <v>502.33333333333331</v>
       </c>
       <c r="P27">
-        <v>90940.66666666669</v>
+        <v>90940.666666666686</v>
       </c>
       <c r="Q27">
         <v>35490667</v>
@@ -2174,7 +2190,7 @@
         <v>1251811667</v>
       </c>
     </row>
-    <row r="28" spans="1:23">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2021</v>
       </c>
@@ -2182,16 +2198,16 @@
         <v>25</v>
       </c>
       <c r="C28">
-        <v>250.44</v>
+        <v>250.39</v>
       </c>
       <c r="D28">
-        <v>235.88</v>
+        <v>235.79</v>
       </c>
       <c r="E28">
-        <v>164.04</v>
+        <v>163.98</v>
       </c>
       <c r="F28">
-        <v>515.92</v>
+        <v>515.91999999999996</v>
       </c>
       <c r="G28" t="s">
         <v>27</v>
@@ -2218,7 +2234,7 @@
         <v>502</v>
       </c>
       <c r="P28">
-        <v>91740.66666666669</v>
+        <v>91740.666666666686</v>
       </c>
       <c r="Q28">
         <v>35435001</v>
@@ -2242,7 +2258,7 @@
         <v>1301976000</v>
       </c>
     </row>
-    <row r="29" spans="1:23">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2021</v>
       </c>
@@ -2250,13 +2266,13 @@
         <v>26</v>
       </c>
       <c r="C29">
-        <v>382.66</v>
+        <v>382.6</v>
       </c>
       <c r="D29">
-        <v>275.84</v>
+        <v>275.74</v>
       </c>
       <c r="E29">
-        <v>183.89</v>
+        <v>183.82</v>
       </c>
       <c r="F29">
         <v>1015.22</v>
@@ -2277,7 +2293,7 @@
         <v>-8.1</v>
       </c>
       <c r="M29">
-        <v>-2.3</v>
+        <v>-2.2999999999999998</v>
       </c>
       <c r="N29">
         <v>33</v>
@@ -2286,7 +2302,7 @@
         <v>501</v>
       </c>
       <c r="P29">
-        <v>92002.66666666669</v>
+        <v>92002.666666666686</v>
       </c>
       <c r="Q29">
         <v>34791000</v>
@@ -2310,7 +2326,7 @@
         <v>1233235667</v>
       </c>
     </row>
-    <row r="30" spans="1:23">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2022</v>
       </c>
@@ -2318,16 +2334,16 @@
         <v>23</v>
       </c>
       <c r="C30">
-        <v>437.41</v>
+        <v>437.37</v>
       </c>
       <c r="D30">
-        <v>411.65</v>
+        <v>411.54</v>
       </c>
       <c r="E30">
-        <v>230.86</v>
+        <v>230.82</v>
       </c>
       <c r="F30">
-        <v>1069.39</v>
+        <v>1069.3900000000001</v>
       </c>
       <c r="G30" t="s">
         <v>27</v>
@@ -2378,7 +2394,7 @@
         <v>1366293000</v>
       </c>
     </row>
-    <row r="31" spans="1:23">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2022</v>
       </c>
@@ -2386,13 +2402,13 @@
         <v>24</v>
       </c>
       <c r="C31">
-        <v>477.66</v>
+        <v>477.47</v>
       </c>
       <c r="D31">
-        <v>580.17</v>
+        <v>579.74</v>
       </c>
       <c r="E31">
-        <v>277.8</v>
+        <v>277.58999999999997</v>
       </c>
       <c r="F31">
         <v>1051.21</v>
@@ -2413,16 +2429,16 @@
         <v>-45.5</v>
       </c>
       <c r="M31">
-        <v>-76.90000000000001</v>
+        <v>-76.900000000000006</v>
       </c>
       <c r="N31">
         <v>-12.6</v>
       </c>
       <c r="O31">
-        <v>509.6666666666667</v>
+        <v>509.66666666666669</v>
       </c>
       <c r="P31">
-        <v>93034.33333333331</v>
+        <v>93034.333333333314</v>
       </c>
       <c r="Q31">
         <v>35705334</v>
@@ -2446,7 +2462,7 @@
         <v>1420781667</v>
       </c>
     </row>
-    <row r="32" spans="1:23">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2022</v>
       </c>
@@ -2454,13 +2470,13 @@
         <v>25</v>
       </c>
       <c r="C32">
-        <v>718.52</v>
+        <v>718.47</v>
       </c>
       <c r="D32">
-        <v>672.51</v>
+        <v>672.34</v>
       </c>
       <c r="E32">
-        <v>256.03</v>
+        <v>255.98</v>
       </c>
       <c r="F32">
         <v>2130.06</v>
@@ -2478,19 +2494,19 @@
         <v>-46.8</v>
       </c>
       <c r="L32">
-        <v>-34.3</v>
+        <v>-34.299999999999997</v>
       </c>
       <c r="M32">
-        <v>-17.4</v>
+        <v>-17.399999999999999</v>
       </c>
       <c r="N32">
         <v>-14.7</v>
       </c>
       <c r="O32">
-        <v>508.6666666666667</v>
+        <v>508.66666666666669</v>
       </c>
       <c r="P32">
-        <v>93600.33333333331</v>
+        <v>93600.333333333314</v>
       </c>
       <c r="Q32">
         <v>35585333</v>
@@ -2514,7 +2530,7 @@
         <v>1400780000</v>
       </c>
     </row>
-    <row r="33" spans="1:23">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2022</v>
       </c>
@@ -2522,13 +2538,13 @@
         <v>26</v>
       </c>
       <c r="C33">
-        <v>432.16</v>
+        <v>432.37</v>
       </c>
       <c r="D33">
-        <v>544.03</v>
+        <v>544.53</v>
       </c>
       <c r="E33">
-        <v>229.38</v>
+        <v>229.63</v>
       </c>
       <c r="F33">
         <v>1011.78</v>
@@ -2543,7 +2559,7 @@
         <v>-27.7</v>
       </c>
       <c r="K33">
-        <v>-77.09999999999999</v>
+        <v>-77.099999999999994</v>
       </c>
       <c r="L33">
         <v>-61.4</v>
@@ -2555,10 +2571,10 @@
         <v>-47</v>
       </c>
       <c r="O33">
-        <v>508.3333333333333</v>
+        <v>508.33333333333331</v>
       </c>
       <c r="P33">
-        <v>93135.33333333331</v>
+        <v>93135.333333333314</v>
       </c>
       <c r="Q33">
         <v>34132667</v>
@@ -2582,7 +2598,7 @@
         <v>1274810999</v>
       </c>
     </row>
-    <row r="34" spans="1:23">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2023</v>
       </c>
@@ -2590,16 +2606,16 @@
         <v>23</v>
       </c>
       <c r="C34">
-        <v>296.18</v>
+        <v>296.26</v>
       </c>
       <c r="D34">
-        <v>344.33</v>
+        <v>344.52</v>
       </c>
       <c r="E34">
-        <v>202.06</v>
+        <v>202.16</v>
       </c>
       <c r="F34">
-        <v>566.3200000000001</v>
+        <v>566.32000000000005</v>
       </c>
       <c r="G34" t="s">
         <v>27</v>
@@ -2614,7 +2630,7 @@
         <v>-59.8</v>
       </c>
       <c r="L34">
-        <v>-40.8</v>
+        <v>-40.799999999999997</v>
       </c>
       <c r="M34">
         <v>21.2</v>
@@ -2650,7 +2666,7 @@
         <v>1324885333</v>
       </c>
     </row>
-    <row r="35" spans="1:23">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2023</v>
       </c>
@@ -2658,13 +2674,13 @@
         <v>24</v>
       </c>
       <c r="C35">
-        <v>234.18</v>
+        <v>234.31</v>
       </c>
       <c r="D35">
-        <v>231.29</v>
+        <v>231.49</v>
       </c>
       <c r="E35">
-        <v>188.52</v>
+        <v>188.68</v>
       </c>
       <c r="F35">
         <v>373.05</v>
@@ -2691,10 +2707,10 @@
         <v>-20.7</v>
       </c>
       <c r="O35">
-        <v>519.6666666666666</v>
+        <v>519.66666666666663</v>
       </c>
       <c r="P35">
-        <v>92435.66666666669</v>
+        <v>92435.666666666686</v>
       </c>
       <c r="Q35">
         <v>34534333</v>
@@ -2718,7 +2734,7 @@
         <v>1235192001</v>
       </c>
     </row>
-    <row r="36" spans="1:23">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2023</v>
       </c>
@@ -2726,13 +2742,13 @@
         <v>25</v>
       </c>
       <c r="C36">
-        <v>241.95</v>
+        <v>241.89</v>
       </c>
       <c r="D36">
-        <v>215.19</v>
+        <v>215.1</v>
       </c>
       <c r="E36">
-        <v>208.69</v>
+        <v>208.61</v>
       </c>
       <c r="F36">
         <v>350.45</v>
@@ -2762,7 +2778,7 @@
         <v>519</v>
       </c>
       <c r="P36">
-        <v>92216.33333333331</v>
+        <v>92216.333333333314</v>
       </c>
       <c r="Q36">
         <v>34677667</v>
@@ -2786,7 +2802,7 @@
         <v>1233688000</v>
       </c>
     </row>
-    <row r="37" spans="1:23">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2023</v>
       </c>
@@ -2794,13 +2810,13 @@
         <v>26</v>
       </c>
       <c r="C37">
-        <v>256.51</v>
+        <v>256.58999999999997</v>
       </c>
       <c r="D37">
-        <v>212.71</v>
+        <v>212.81</v>
       </c>
       <c r="E37">
-        <v>203.23</v>
+        <v>203.33</v>
       </c>
       <c r="F37">
         <v>430.58</v>
@@ -2815,7 +2831,7 @@
         <v>-32.6</v>
       </c>
       <c r="K37">
-        <v>-67.40000000000001</v>
+        <v>-67.400000000000006</v>
       </c>
       <c r="L37">
         <v>-43.2</v>
@@ -2830,7 +2846,7 @@
         <v>518</v>
       </c>
       <c r="P37">
-        <v>91727.66666666669</v>
+        <v>91727.666666666686</v>
       </c>
       <c r="Q37">
         <v>33598333</v>
@@ -2854,7 +2870,7 @@
         <v>1156011000</v>
       </c>
     </row>
-    <row r="38" spans="1:23">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2024</v>
       </c>
@@ -2862,16 +2878,16 @@
         <v>23</v>
       </c>
       <c r="C38">
-        <v>219.53</v>
+        <v>219.51</v>
       </c>
       <c r="D38">
-        <v>188.24</v>
+        <v>188.21</v>
       </c>
       <c r="E38">
-        <v>198.8</v>
+        <v>198.78</v>
       </c>
       <c r="F38">
-        <v>291.47</v>
+        <v>291.47000000000003</v>
       </c>
       <c r="G38" t="s">
         <v>27</v>
@@ -2898,7 +2914,7 @@
         <v>515</v>
       </c>
       <c r="P38">
-        <v>91036.66666666669</v>
+        <v>91036.666666666686</v>
       </c>
       <c r="Q38">
         <v>36093999</v>
@@ -2922,7 +2938,7 @@
         <v>1269569666</v>
       </c>
     </row>
-    <row r="39" spans="1:23">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2024</v>
       </c>
@@ -2936,7 +2952,7 @@
         <v>206.2</v>
       </c>
       <c r="E39">
-        <v>208.49</v>
+        <v>208.5</v>
       </c>
       <c r="F39">
         <v>335.66</v>
@@ -2954,7 +2970,7 @@
         <v>-52.9</v>
       </c>
       <c r="L39">
-        <v>-19.4</v>
+        <v>-19.399999999999999</v>
       </c>
       <c r="M39">
         <v>-16.3</v>
@@ -2963,7 +2979,7 @@
         <v>-58.7</v>
       </c>
       <c r="O39">
-        <v>520.3333333333334</v>
+        <v>520.33333333333337</v>
       </c>
       <c r="P39">
         <v>91111</v>
@@ -2990,7 +3006,7 @@
         <v>1250462000</v>
       </c>
     </row>
-    <row r="40" spans="1:23">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2024</v>
       </c>
@@ -2998,13 +3014,13 @@
         <v>25</v>
       </c>
       <c r="C40">
-        <v>233.41</v>
+        <v>233.47</v>
       </c>
       <c r="D40">
-        <v>207.63</v>
+        <v>207.69</v>
       </c>
       <c r="E40">
-        <v>189.23</v>
+        <v>189.3</v>
       </c>
       <c r="F40">
         <v>374.65</v>
@@ -3019,7 +3035,7 @@
         <v>-13.7</v>
       </c>
       <c r="K40">
-        <v>-39.2</v>
+        <v>-39.200000000000003</v>
       </c>
       <c r="L40">
         <v>-11</v>
@@ -3034,7 +3050,7 @@
         <v>519</v>
       </c>
       <c r="P40">
-        <v>91501.33333333331</v>
+        <v>91501.333333333314</v>
       </c>
       <c r="Q40">
         <v>34813000</v>
@@ -3058,7 +3074,7 @@
         <v>1266318001</v>
       </c>
     </row>
-    <row r="41" spans="1:23">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2024</v>
       </c>
@@ -3066,13 +3082,13 @@
         <v>26</v>
       </c>
       <c r="C41">
-        <v>248.68</v>
+        <v>248.57</v>
       </c>
       <c r="D41">
-        <v>213.23</v>
+        <v>213.06</v>
       </c>
       <c r="E41">
-        <v>183.15</v>
+        <v>183.01</v>
       </c>
       <c r="F41">
         <v>457.27</v>
@@ -3099,10 +3115,10 @@
         <v>-53.8</v>
       </c>
       <c r="O41">
-        <v>518.3333333333334</v>
+        <v>518.33333333333337</v>
       </c>
       <c r="P41">
-        <v>91317.66666666669</v>
+        <v>91317.666666666686</v>
       </c>
       <c r="Q41">
         <v>33354000</v>
@@ -3126,7 +3142,7 @@
         <v>1171667333</v>
       </c>
     </row>
-    <row r="42" spans="1:23">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2025</v>
       </c>
@@ -3134,13 +3150,13 @@
         <v>23</v>
       </c>
       <c r="C42">
-        <v>258.83</v>
+        <v>258.89999999999998</v>
       </c>
       <c r="D42">
-        <v>176.03</v>
+        <v>176.1</v>
       </c>
       <c r="E42">
-        <v>188.2</v>
+        <v>188.3</v>
       </c>
       <c r="F42">
         <v>496.95</v>
@@ -3155,46 +3171,46 @@
         <v>-17.39130434782609</v>
       </c>
       <c r="K42">
-        <v>-43.47826086956522</v>
+        <v>-43.478260869565219</v>
       </c>
       <c r="L42">
-        <v>-9.890109890109891</v>
+        <v>-9.8901098901098905</v>
       </c>
       <c r="M42">
-        <v>5.434782608695652</v>
+        <v>5.4347826086956523</v>
       </c>
       <c r="N42">
-        <v>-66.304347826087</v>
+        <v>-66.304347826086996</v>
       </c>
       <c r="O42">
-        <v>507.3333333333333</v>
+        <v>507.33333333333331</v>
       </c>
       <c r="P42">
-        <v>90690.33333333331</v>
+        <v>90346.666666666686</v>
       </c>
       <c r="Q42">
-        <v>35355333</v>
+        <v>35452000</v>
       </c>
       <c r="R42">
-        <v>1096558666</v>
+        <v>1092442000</v>
       </c>
       <c r="S42">
-        <v>6328775999</v>
+        <v>6332096000</v>
       </c>
       <c r="T42">
-        <v>3305871667</v>
+        <v>3309552333</v>
       </c>
       <c r="U42">
-        <v>3022903667</v>
+        <v>3022544667</v>
       </c>
       <c r="V42">
-        <v>1774222001</v>
+        <v>1775157334</v>
       </c>
       <c r="W42">
-        <v>1248682334</v>
-      </c>
-    </row>
-    <row r="43" spans="1:23">
+        <v>1247385666</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2025</v>
       </c>
@@ -3202,13 +3218,13 @@
         <v>24</v>
       </c>
       <c r="C43">
-        <v>206.45</v>
+        <v>206.44</v>
       </c>
       <c r="D43">
-        <v>152.44</v>
+        <v>152.43</v>
       </c>
       <c r="E43">
-        <v>155.37</v>
+        <v>155.36000000000001</v>
       </c>
       <c r="F43">
         <v>376.9</v>
@@ -3226,7 +3242,7 @@
         <v>-32.4</v>
       </c>
       <c r="L43">
-        <v>-8.699999999999999</v>
+        <v>-8.6999999999999993</v>
       </c>
       <c r="M43">
         <v>-6.7</v>
@@ -3238,31 +3254,31 @@
         <v>509</v>
       </c>
       <c r="P43">
-        <v>90306.66666666669</v>
+        <v>90280</v>
       </c>
       <c r="Q43">
-        <v>34012667</v>
+        <v>34001333</v>
       </c>
       <c r="R43">
-        <v>1178328666</v>
+        <v>1178298667</v>
       </c>
       <c r="S43">
-        <v>6355352000</v>
+        <v>6334088666</v>
       </c>
       <c r="T43">
-        <v>3367534333</v>
+        <v>3357510667</v>
       </c>
       <c r="U43">
-        <v>2987817666</v>
+        <v>2976577999</v>
       </c>
       <c r="V43">
-        <v>1757211000</v>
+        <v>1750786667</v>
       </c>
       <c r="W43">
-        <v>1230606667</v>
-      </c>
-    </row>
-    <row r="44" spans="1:23">
+        <v>1225790667</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2025</v>
       </c>
@@ -3270,13 +3286,13 @@
         <v>25</v>
       </c>
       <c r="C44">
-        <v>198.46</v>
+        <v>198.5</v>
       </c>
       <c r="D44">
-        <v>155.97</v>
+        <v>156.02000000000001</v>
       </c>
       <c r="E44">
-        <v>154.01</v>
+        <v>154.06</v>
       </c>
       <c r="F44">
         <v>345.47</v>
@@ -3294,7 +3310,7 @@
         <v>-4.45</v>
       </c>
       <c r="K44">
-        <v>-26.67000000000001</v>
+        <v>-26.670000000000009</v>
       </c>
       <c r="L44">
         <v>-18.39</v>
@@ -3306,40 +3322,52 @@
         <v>-40</v>
       </c>
       <c r="O44">
-        <v>509.6666666666667</v>
+        <v>509.66666666666669</v>
       </c>
       <c r="P44">
-        <v>90814.66666666669</v>
+        <v>90781.666666666686</v>
       </c>
       <c r="Q44">
-        <v>34594000</v>
+        <v>34595333</v>
       </c>
       <c r="R44">
-        <v>1121252666</v>
+        <v>1119684667</v>
       </c>
       <c r="S44">
-        <v>6339248333</v>
+        <v>6332476000</v>
       </c>
       <c r="T44">
-        <v>3419494000</v>
+        <v>3420780000</v>
       </c>
       <c r="U44">
-        <v>2919754334</v>
+        <v>2911696333</v>
       </c>
       <c r="V44">
-        <v>1683136667</v>
+        <v>1679849000</v>
       </c>
       <c r="W44">
-        <v>1236617667</v>
-      </c>
-    </row>
-    <row r="45" spans="1:23">
+        <v>1231848666</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2025</v>
       </c>
       <c r="B45" t="s">
         <v>26</v>
       </c>
+      <c r="C45">
+        <v>184.44</v>
+      </c>
+      <c r="D45">
+        <v>151.35</v>
+      </c>
+      <c r="E45">
+        <v>143.11000000000001</v>
+      </c>
+      <c r="F45">
+        <v>319.2</v>
+      </c>
       <c r="G45" t="s">
         <v>27</v>
       </c>
@@ -3365,34 +3393,34 @@
         <v>-55</v>
       </c>
       <c r="O45">
-        <v>509.6666666666667</v>
+        <v>509.66666666666669</v>
       </c>
       <c r="P45">
-        <v>90523.33333333331</v>
+        <v>90488.333333333314</v>
       </c>
       <c r="Q45">
-        <v>33269333</v>
+        <v>33213000</v>
       </c>
       <c r="R45">
-        <v>1270684666</v>
+        <v>1269489667</v>
       </c>
       <c r="S45">
-        <v>5814783000</v>
+        <v>5802778667</v>
       </c>
       <c r="T45">
-        <v>3043982667</v>
+        <v>3035254666</v>
       </c>
       <c r="U45">
-        <v>2770801334</v>
+        <v>2767523999</v>
       </c>
       <c r="V45">
-        <v>1611543333</v>
+        <v>1609410333</v>
       </c>
       <c r="W45">
-        <v>1159257000</v>
-      </c>
-    </row>
-    <row r="46" spans="1:23">
+        <v>1158113667</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2026</v>
       </c>
@@ -3422,6 +3450,65 @@
       </c>
       <c r="N46">
         <v>-67.89</v>
+      </c>
+      <c r="O46">
+        <v>167.66666666666671</v>
+      </c>
+      <c r="P46">
+        <v>29943</v>
+      </c>
+      <c r="Q46">
+        <v>11480333</v>
+      </c>
+      <c r="R46">
+        <v>369736333</v>
+      </c>
+      <c r="S46">
+        <v>1982539333</v>
+      </c>
+      <c r="T46">
+        <v>1023429667</v>
+      </c>
+      <c r="U46">
+        <v>959109000</v>
+      </c>
+      <c r="V46">
+        <v>577660000</v>
+      </c>
+      <c r="W46">
+        <v>381449667</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>2026</v>
+      </c>
+      <c r="B47" t="s">
+        <v>24</v>
+      </c>
+      <c r="G47" t="s">
+        <v>27</v>
+      </c>
+      <c r="H47" t="s">
+        <v>28</v>
+      </c>
+      <c r="I47">
+        <v>-3.8100000000000018</v>
+      </c>
+      <c r="J47">
+        <v>-17.149999999999999</v>
+      </c>
+      <c r="K47">
+        <v>-44.77</v>
+      </c>
+      <c r="L47">
+        <v>-17.47</v>
+      </c>
+      <c r="M47">
+        <v>-85.71</v>
+      </c>
+      <c r="N47">
+        <v>-51.43</v>
       </c>
     </row>
   </sheetData>

--- a/data/IK_Konj+Destatis_HWWI.xlsx
+++ b/data/IK_Konj+Destatis_HWWI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l.mueller\Documents\FileCloud\Team Folders\IK_Server\Wirtschaft\statistische Daten\ik-dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ACD8EA7-D094-4FAF-BF34-32568E28BE0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{125ECD78-6DF2-4889-8BBE-22852E1327DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="2370" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3451,33 +3451,6 @@
       <c r="N46">
         <v>-67.89</v>
       </c>
-      <c r="O46">
-        <v>167.66666666666671</v>
-      </c>
-      <c r="P46">
-        <v>29943</v>
-      </c>
-      <c r="Q46">
-        <v>11480333</v>
-      </c>
-      <c r="R46">
-        <v>369736333</v>
-      </c>
-      <c r="S46">
-        <v>1982539333</v>
-      </c>
-      <c r="T46">
-        <v>1023429667</v>
-      </c>
-      <c r="U46">
-        <v>959109000</v>
-      </c>
-      <c r="V46">
-        <v>577660000</v>
-      </c>
-      <c r="W46">
-        <v>381449667</v>
-      </c>
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A47">

--- a/data/IK_Konj+Destatis_HWWI.xlsx
+++ b/data/IK_Konj+Destatis_HWWI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l.mueller\Documents\FileCloud\Team Folders\IK_Server\Wirtschaft\statistische Daten\ik-dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{125ECD78-6DF2-4889-8BBE-22852E1327DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B03A0170-B26B-4708-9439-1F5399E0DFD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="2370" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="29">
   <si>
     <t>Jahr</t>
   </si>
@@ -474,8 +474,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W47"/>
+  <dimension ref="A1:W49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="15" max="16" width="12" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="29.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -3427,6 +3432,18 @@
       <c r="B46" t="s">
         <v>23</v>
       </c>
+      <c r="C46">
+        <v>233.5</v>
+      </c>
+      <c r="D46">
+        <v>170.25</v>
+      </c>
+      <c r="E46">
+        <v>176.51</v>
+      </c>
+      <c r="F46">
+        <v>424.56</v>
+      </c>
       <c r="G46" t="s">
         <v>27</v>
       </c>
@@ -3450,6 +3467,33 @@
       </c>
       <c r="N46">
         <v>-67.89</v>
+      </c>
+      <c r="O46">
+        <v>505.33333333333331</v>
+      </c>
+      <c r="P46">
+        <v>89937</v>
+      </c>
+      <c r="Q46">
+        <v>35393999</v>
+      </c>
+      <c r="R46">
+        <v>1119699999</v>
+      </c>
+      <c r="S46">
+        <v>6365473333</v>
+      </c>
+      <c r="T46">
+        <v>3323429001</v>
+      </c>
+      <c r="U46">
+        <v>3042044333</v>
+      </c>
+      <c r="V46">
+        <v>1815971667</v>
+      </c>
+      <c r="W46">
+        <v>1226073334</v>
       </c>
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.25">
@@ -3482,6 +3526,52 @@
       </c>
       <c r="N47">
         <v>-51.43</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>2026</v>
+      </c>
+      <c r="B48" t="s">
+        <v>25</v>
+      </c>
+      <c r="G48" t="s">
+        <v>27</v>
+      </c>
+      <c r="H48" t="s">
+        <v>28</v>
+      </c>
+      <c r="I48">
+        <v>-19.559999999999999</v>
+      </c>
+      <c r="J48">
+        <v>-14.13</v>
+      </c>
+      <c r="K48">
+        <v>-39.130000000000003</v>
+      </c>
+      <c r="L48">
+        <v>-15.91</v>
+      </c>
+      <c r="M48">
+        <v>33.69</v>
+      </c>
+      <c r="N48">
+        <v>-54.350000000000009</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>2026</v>
+      </c>
+      <c r="B49" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" t="s">
+        <v>27</v>
+      </c>
+      <c r="H49" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
